--- a/order_forms/024_nutrition_supplement_order_form--order_forms.xlsx
+++ b/order_forms/024_nutrition_supplement_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'supplement_1',_'value':_'supplement_1'}</t>
+          <t>supplement_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Supplement 1', 'value': 'supplement_1'}</t>
+          <t>Supplement 1</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'supplement_2',_'value':_'supplement_2'}</t>
+          <t>supplement_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Supplement 2', 'value': 'supplement_2'}</t>
+          <t>Supplement 2</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'supplement_3',_'value':_'supplement_3'}</t>
+          <t>supplement_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Supplement 3', 'value': 'supplement_3'}</t>
+          <t>Supplement 3</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer', 'value': 'bank_transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'paid',_'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Paid', 'value': 'paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'refunded',_'value':_'refunded'}</t>
+          <t>refunded</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Refunded', 'value': 'refunded'}</t>
+          <t>Refunded</t>
         </is>
       </c>
     </row>
